--- a/publish/hub/docs/NutriSync-Costes-SaaS-y-Esfuerzo-Founders-2026-08.xlsx
+++ b/publish/hub/docs/NutriSync-Costes-SaaS-y-Esfuerzo-Founders-2026-08.xlsx
@@ -1311,6 +1311,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -1716,6 +1717,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1779,6 +1781,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -2248,7 +2251,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>1.288 €/día → 19.964,00 € ≈ $22.959 · fase desarrollo → capitalization_review (IAS 38)</t>
+          <t>888 €/día → 13.764,00 € ≈ $15.829 · fase desarrollo → capitalization_review (IAS 38)</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
